--- a/data/sample-data.xlsx
+++ b/data/sample-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\roqore\artisan-coffee-co\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E7C51E-92BF-48D8-8768-8D196F4DD916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100375A0-7A90-4181-987B-A11E4C216A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{432A8DC7-3C39-436D-BC34-D70F3C1732F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="12" xr2:uid="{432A8DC7-3C39-436D-BC34-D70F3C1732F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
@@ -1939,11 +1939,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2266,8 +2266,8 @@
     <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -2291,10 +2291,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2329,11 +2329,11 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="5">
         <v>31121</v>
       </c>
-      <c r="G2">
-        <v>45306</v>
+      <c r="G2" s="6">
+        <v>45847</v>
       </c>
       <c r="H2">
         <v>247</v>
@@ -2367,11 +2367,11 @@
       <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
         <v>33807</v>
       </c>
-      <c r="G3">
-        <v>45325</v>
+      <c r="G3" s="6">
+        <v>45847</v>
       </c>
       <c r="H3">
         <v>89</v>
@@ -2405,11 +2405,11 @@
       <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="5">
         <v>32455</v>
       </c>
-      <c r="G4">
-        <v>45319</v>
+      <c r="G4" s="6">
+        <v>45847</v>
       </c>
       <c r="H4">
         <v>156</v>
@@ -2443,11 +2443,11 @@
       <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="5">
         <v>27526</v>
       </c>
-      <c r="G5">
-        <v>45250</v>
+      <c r="G5" s="6">
+        <v>45847</v>
       </c>
       <c r="H5">
         <v>412</v>
@@ -2481,11 +2481,11 @@
       <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5">
         <v>33146</v>
       </c>
-      <c r="G6">
-        <v>45361</v>
+      <c r="G6" s="6">
+        <v>45847</v>
       </c>
       <c r="H6">
         <v>67</v>
@@ -2519,11 +2519,11 @@
       <c r="E7" t="s">
         <v>46</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="5">
         <v>30303</v>
       </c>
-      <c r="G7">
-        <v>45296</v>
+      <c r="G7" s="6">
+        <v>45847</v>
       </c>
       <c r="H7">
         <v>198</v>
@@ -2557,11 +2557,11 @@
       <c r="E8" t="s">
         <v>51</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="5">
         <v>34814</v>
       </c>
-      <c r="G8">
-        <v>45336</v>
+      <c r="G8" s="6">
+        <v>45847</v>
       </c>
       <c r="H8">
         <v>134</v>
@@ -2595,11 +2595,11 @@
       <c r="E9" t="s">
         <v>56</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="5">
         <v>31996</v>
       </c>
-      <c r="G9">
-        <v>45313</v>
+      <c r="G9" s="6">
+        <v>45847</v>
       </c>
       <c r="H9">
         <v>89</v>
@@ -2642,11 +2642,11 @@
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2665,7 +2665,7 @@
       <c r="E1" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -2674,10 +2674,10 @@
       <c r="H1" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>392</v>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       <c r="E2" t="s">
         <v>397</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="5">
         <v>45153</v>
       </c>
       <c r="G2" t="s">
@@ -2706,10 +2706,10 @@
       <c r="H2" t="s">
         <v>399</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="5">
         <v>45444</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="5">
         <v>45474</v>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       <c r="E3" t="s">
         <v>404</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
         <v>45170</v>
       </c>
       <c r="G3" t="s">
@@ -2738,10 +2738,10 @@
       <c r="H3" t="s">
         <v>399</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>45427</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>45458</v>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       <c r="E4" t="s">
         <v>410</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="5">
         <v>45170</v>
       </c>
       <c r="G4" t="s">
@@ -2770,10 +2770,10 @@
       <c r="H4" t="s">
         <v>399</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>45453</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>45483</v>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       <c r="E5" t="s">
         <v>414</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="5">
         <v>45184</v>
       </c>
       <c r="G5" t="s">
@@ -2802,10 +2802,10 @@
       <c r="H5" t="s">
         <v>399</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>45448</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>45478</v>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       <c r="E6" t="s">
         <v>420</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5">
         <v>45170</v>
       </c>
       <c r="G6" t="s">
@@ -2834,10 +2834,10 @@
       <c r="H6" t="s">
         <v>399</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>45444</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>45474</v>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       <c r="E7" t="s">
         <v>425</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="5">
         <v>45170</v>
       </c>
       <c r="G7" t="s">
@@ -2866,10 +2866,10 @@
       <c r="H7" t="s">
         <v>399</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>45444</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>45474</v>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -3150,7 +3150,7 @@
       <c r="A1" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>450</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -3176,7 +3176,7 @@
       <c r="A2" t="s">
         <v>455</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>45444</v>
       </c>
       <c r="C2" t="s">
@@ -3202,7 +3202,7 @@
       <c r="A3" t="s">
         <v>460</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>45448</v>
       </c>
       <c r="C3" t="s">
@@ -3228,7 +3228,7 @@
       <c r="A4" t="s">
         <v>465</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>45453</v>
       </c>
       <c r="C4" t="s">
@@ -3254,7 +3254,7 @@
       <c r="A5" t="s">
         <v>469</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>45455</v>
       </c>
       <c r="C5" t="s">
@@ -3280,7 +3280,7 @@
       <c r="A6" t="s">
         <v>472</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>45458</v>
       </c>
       <c r="C6" t="s">
@@ -3306,7 +3306,7 @@
       <c r="A7" t="s">
         <v>476</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>45461</v>
       </c>
       <c r="C7" t="s">
@@ -3332,7 +3332,7 @@
       <c r="A8" t="s">
         <v>481</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>45463</v>
       </c>
       <c r="C8" t="s">
@@ -3367,8 +3367,8 @@
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
@@ -3386,10 +3386,10 @@
       <c r="C1" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>488</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -3418,10 +3418,10 @@
       <c r="C2" t="s">
         <v>496</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="5">
         <v>45444</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5">
         <v>45535</v>
       </c>
       <c r="F2">
@@ -3450,10 +3450,10 @@
       <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="5">
         <v>45444</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="5">
         <v>45473</v>
       </c>
       <c r="F3">
@@ -3482,10 +3482,10 @@
       <c r="C4" t="s">
         <v>496</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="5">
         <v>45453</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <v>45459</v>
       </c>
       <c r="F4">
@@ -3514,10 +3514,10 @@
       <c r="C5" t="s">
         <v>506</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="5">
         <v>45444</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="5">
         <v>45504</v>
       </c>
       <c r="F5">
@@ -3668,7 +3668,7 @@
     <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
@@ -3700,7 +3700,7 @@
       <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -3741,7 +3741,7 @@
       <c r="H2" t="s">
         <v>78</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="5">
         <v>45306</v>
       </c>
       <c r="J2">
@@ -3782,7 +3782,7 @@
       <c r="H3" t="s">
         <v>88</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>45342</v>
       </c>
       <c r="J3">
@@ -3823,7 +3823,7 @@
       <c r="H4" t="s">
         <v>97</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>45321</v>
       </c>
       <c r="J4">
@@ -3864,7 +3864,7 @@
       <c r="H5" t="s">
         <v>106</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>45332</v>
       </c>
       <c r="J5">
@@ -3905,7 +3905,7 @@
       <c r="H6" t="s">
         <v>116</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>45356</v>
       </c>
       <c r="J6">
@@ -3946,7 +3946,7 @@
       <c r="H7" t="s">
         <v>124</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>45347</v>
       </c>
       <c r="J7">
@@ -3987,7 +3987,7 @@
       <c r="H8" t="s">
         <v>132</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>45311</v>
       </c>
       <c r="J8">
@@ -4028,7 +4028,7 @@
       <c r="H9" t="s">
         <v>139</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>45337</v>
       </c>
       <c r="J9">
@@ -4060,7 +4060,7 @@
     <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -4084,7 +4084,7 @@
       <c r="F1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>146</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -4113,7 +4113,7 @@
       <c r="F2">
         <v>0.2</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="5">
         <v>45311</v>
       </c>
       <c r="H2" t="s">
@@ -4142,7 +4142,7 @@
       <c r="F3">
         <v>0.22</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="5">
         <v>45347</v>
       </c>
       <c r="H3" t="s">
@@ -4171,7 +4171,7 @@
       <c r="F4">
         <v>0.21</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="5">
         <v>45327</v>
       </c>
       <c r="H4" t="s">
@@ -4200,7 +4200,7 @@
       <c r="F5">
         <v>0.23</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="5">
         <v>45337</v>
       </c>
       <c r="H5" t="s">
@@ -4229,7 +4229,7 @@
       <c r="F6">
         <v>0.25</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="5">
         <v>45361</v>
       </c>
       <c r="H6" t="s">
@@ -4258,7 +4258,7 @@
       <c r="F7">
         <v>0.22</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="5">
         <v>45352</v>
       </c>
       <c r="H7" t="s">
@@ -4287,7 +4287,7 @@
       <c r="F8">
         <v>0.18</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="5">
         <v>45316</v>
       </c>
       <c r="H8" t="s">
@@ -4316,7 +4316,7 @@
       <c r="F9">
         <v>0.21</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="5">
         <v>45342</v>
       </c>
       <c r="H9" t="s">
@@ -4796,9 +4796,9 @@
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4818,13 +4818,13 @@
       <c r="E1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>242</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -4847,13 +4847,13 @@
       <c r="E2">
         <v>22</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="5">
         <v>45462</v>
       </c>
       <c r="G2" t="s">
         <v>245</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>45519</v>
       </c>
       <c r="I2" t="s">
@@ -4876,13 +4876,13 @@
       <c r="E3">
         <v>17</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
         <v>45462</v>
       </c>
       <c r="G3" t="s">
         <v>245</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>45524</v>
       </c>
       <c r="I3" t="s">
@@ -4905,13 +4905,13 @@
       <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="5">
         <v>45462</v>
       </c>
       <c r="G4" t="s">
         <v>245</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>45514</v>
       </c>
       <c r="I4" t="s">
@@ -4934,13 +4934,13 @@
       <c r="E5">
         <v>32</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="5">
         <v>45462</v>
       </c>
       <c r="G5" t="s">
         <v>245</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>45529</v>
       </c>
       <c r="I5" t="s">
@@ -4963,13 +4963,13 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5">
         <v>45462</v>
       </c>
       <c r="G6" t="s">
         <v>245</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>45536</v>
       </c>
       <c r="I6" t="s">
@@ -4992,13 +4992,13 @@
       <c r="E7">
         <v>12</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="5">
         <v>45463</v>
       </c>
       <c r="G7" t="s">
         <v>245</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>45462</v>
       </c>
       <c r="I7" t="s">
@@ -5021,13 +5021,13 @@
       <c r="E8">
         <v>7</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="5">
         <v>45462</v>
       </c>
       <c r="G8" t="s">
         <v>258</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>45465</v>
       </c>
       <c r="I8" t="s">
@@ -5050,13 +5050,13 @@
       <c r="E9">
         <v>15.5</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="5">
         <v>45463</v>
       </c>
       <c r="G9" t="s">
         <v>258</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>45672</v>
       </c>
       <c r="I9" t="s">
@@ -5079,13 +5079,13 @@
       <c r="E10">
         <v>17.3</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="5">
         <v>45463</v>
       </c>
       <c r="G10" t="s">
         <v>258</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>45708</v>
       </c>
       <c r="I10" t="s">
@@ -5108,13 +5108,13 @@
       <c r="E11">
         <v>15.7</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="5">
         <v>45463</v>
       </c>
       <c r="G11" t="s">
         <v>258</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>45721</v>
       </c>
       <c r="I11" t="s">
@@ -5137,7 +5137,7 @@
     <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="35.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -5161,7 +5161,7 @@
       <c r="F1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>269</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -5190,7 +5190,7 @@
       <c r="F2">
         <v>25</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="5">
         <v>45170</v>
       </c>
       <c r="H2" t="s">
@@ -5219,7 +5219,7 @@
       <c r="F3">
         <v>18.5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="5">
         <v>45214</v>
       </c>
       <c r="H3" t="s">
@@ -5248,7 +5248,7 @@
       <c r="F4">
         <v>16.75</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="5">
         <v>45231</v>
       </c>
       <c r="H4" t="s">
@@ -5277,7 +5277,7 @@
       <c r="F5">
         <v>15.5</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="5">
         <v>45306</v>
       </c>
       <c r="H5" t="s">
@@ -5306,7 +5306,7 @@
       <c r="F6">
         <v>15</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="5">
         <v>45352</v>
       </c>
       <c r="H6" t="s">
@@ -5335,7 +5335,7 @@
       <c r="F7">
         <v>15</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="5">
         <v>45383</v>
       </c>
       <c r="H7" t="s">
@@ -5365,7 +5365,7 @@
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
@@ -5422,8 +5422,8 @@
       <c r="B2" s="3">
         <v>1001</v>
       </c>
-      <c r="C2" s="5">
-        <v>45837</v>
+      <c r="C2" s="6">
+        <v>45847</v>
       </c>
       <c r="D2" s="3">
         <v>0.32291666699999999</v>
@@ -5460,8 +5460,8 @@
       <c r="B3" s="3">
         <v>1004</v>
       </c>
-      <c r="C3" s="5">
-        <v>45837</v>
+      <c r="C3" s="6">
+        <v>45847</v>
       </c>
       <c r="D3" s="3">
         <v>0.34375</v>
@@ -5498,8 +5498,8 @@
       <c r="B4" s="3">
         <v>1002</v>
       </c>
-      <c r="C4" s="5">
-        <v>45837</v>
+      <c r="C4" s="6">
+        <v>45847</v>
       </c>
       <c r="D4" s="3">
         <v>0.35416666699999999</v>
@@ -5536,8 +5536,8 @@
       <c r="B5" s="3">
         <v>1006</v>
       </c>
-      <c r="C5" s="5">
-        <v>45837</v>
+      <c r="C5" s="6">
+        <v>45847</v>
       </c>
       <c r="D5" s="3">
         <v>0.375</v>
@@ -5574,8 +5574,8 @@
       <c r="B6" s="3">
         <v>1003</v>
       </c>
-      <c r="C6" s="5">
-        <v>45837</v>
+      <c r="C6" s="6">
+        <v>45847</v>
       </c>
       <c r="D6" s="3">
         <v>0.38541666699999999</v>
@@ -5612,8 +5612,8 @@
       <c r="B7" s="3">
         <v>1007</v>
       </c>
-      <c r="C7" s="5">
-        <v>45837</v>
+      <c r="C7" s="6">
+        <v>45847</v>
       </c>
       <c r="D7" s="3">
         <v>0.4375</v>
@@ -5650,8 +5650,8 @@
       <c r="B8" s="3">
         <v>1005</v>
       </c>
-      <c r="C8" s="5">
-        <v>45837</v>
+      <c r="C8" s="6">
+        <v>45847</v>
       </c>
       <c r="D8" s="3">
         <v>0.48958333300000001</v>
@@ -5688,8 +5688,8 @@
       <c r="B9" s="3">
         <v>1001</v>
       </c>
-      <c r="C9" s="5">
-        <v>45837</v>
+      <c r="C9" s="6">
+        <v>45847</v>
       </c>
       <c r="D9" s="3">
         <v>0.59722222199999997</v>
@@ -5726,8 +5726,8 @@
       <c r="B10" s="3">
         <v>1002</v>
       </c>
-      <c r="C10" s="5">
-        <v>45837</v>
+      <c r="C10" s="6">
+        <v>45848</v>
       </c>
       <c r="D10" s="3">
         <v>0.61111111100000004</v>
@@ -5764,8 +5764,8 @@
       <c r="B11" s="3">
         <v>1006</v>
       </c>
-      <c r="C11" s="5">
-        <v>45837</v>
+      <c r="C11" s="6">
+        <v>45848</v>
       </c>
       <c r="D11" s="3">
         <v>0.625</v>
@@ -5802,8 +5802,8 @@
       <c r="B12" s="3">
         <v>1007</v>
       </c>
-      <c r="C12" s="5">
-        <v>45838</v>
+      <c r="C12" s="6">
+        <v>45848</v>
       </c>
       <c r="D12" s="3">
         <v>0.63888888899999996</v>
@@ -5840,8 +5840,8 @@
       <c r="B13" s="3">
         <v>1003</v>
       </c>
-      <c r="C13" s="5">
-        <v>45838</v>
+      <c r="C13" s="6">
+        <v>45848</v>
       </c>
       <c r="D13" s="3">
         <v>0.65277777800000003</v>
@@ -5878,8 +5878,8 @@
       <c r="B14" s="3">
         <v>1004</v>
       </c>
-      <c r="C14" s="5">
-        <v>45838</v>
+      <c r="C14" s="6">
+        <v>45848</v>
       </c>
       <c r="D14" s="3">
         <v>0.66666666699999999</v>
@@ -5916,8 +5916,8 @@
       <c r="B15" s="3">
         <v>1005</v>
       </c>
-      <c r="C15" s="5">
-        <v>45838</v>
+      <c r="C15" s="6">
+        <v>45848</v>
       </c>
       <c r="D15" s="3">
         <v>0.68055555599999995</v>
@@ -5954,8 +5954,8 @@
       <c r="B16" s="3">
         <v>1001</v>
       </c>
-      <c r="C16" s="5">
-        <v>45838</v>
+      <c r="C16" s="6">
+        <v>45848</v>
       </c>
       <c r="D16" s="3">
         <v>0.69444444400000005</v>
@@ -5992,8 +5992,8 @@
       <c r="B17" s="3">
         <v>1002</v>
       </c>
-      <c r="C17" s="5">
-        <v>45838</v>
+      <c r="C17" s="6">
+        <v>45849</v>
       </c>
       <c r="D17" s="3">
         <v>0.70833333300000001</v>
@@ -6030,8 +6030,8 @@
       <c r="B18" s="3">
         <v>1003</v>
       </c>
-      <c r="C18" s="5">
-        <v>45838</v>
+      <c r="C18" s="6">
+        <v>45849</v>
       </c>
       <c r="D18" s="3">
         <v>0.72222222199999997</v>
@@ -6068,8 +6068,8 @@
       <c r="B19" s="3">
         <v>1006</v>
       </c>
-      <c r="C19" s="5">
-        <v>45838</v>
+      <c r="C19" s="6">
+        <v>45849</v>
       </c>
       <c r="D19" s="3">
         <v>0.73611111100000004</v>
@@ -6106,8 +6106,8 @@
       <c r="B20" s="3">
         <v>1004</v>
       </c>
-      <c r="C20" s="5">
-        <v>45838</v>
+      <c r="C20" s="6">
+        <v>45849</v>
       </c>
       <c r="D20" s="3">
         <v>0.75</v>
@@ -6144,8 +6144,8 @@
       <c r="B21" s="3">
         <v>1007</v>
       </c>
-      <c r="C21" s="5">
-        <v>45838</v>
+      <c r="C21" s="6">
+        <v>45849</v>
       </c>
       <c r="D21" s="3">
         <v>0.76388888899999996</v>
@@ -6182,8 +6182,8 @@
       <c r="B22" s="3">
         <v>1001</v>
       </c>
-      <c r="C22" s="5">
-        <v>45838</v>
+      <c r="C22" s="6">
+        <v>45849</v>
       </c>
       <c r="D22" s="3">
         <v>0.77777777800000003</v>
@@ -6220,8 +6220,8 @@
       <c r="B23" s="3">
         <v>1005</v>
       </c>
-      <c r="C23" s="5">
-        <v>45838</v>
+      <c r="C23" s="6">
+        <v>45849</v>
       </c>
       <c r="D23" s="3">
         <v>0.79166666699999999</v>
@@ -6258,8 +6258,8 @@
       <c r="B24" s="3">
         <v>1002</v>
       </c>
-      <c r="C24" s="5">
-        <v>45839</v>
+      <c r="C24" s="6">
+        <v>45849</v>
       </c>
       <c r="D24" s="3">
         <v>0.80555555599999995</v>
@@ -6296,8 +6296,8 @@
       <c r="B25" s="3">
         <v>1006</v>
       </c>
-      <c r="C25" s="5">
-        <v>45839</v>
+      <c r="C25" s="6">
+        <v>45850</v>
       </c>
       <c r="D25" s="3">
         <v>0.81944444400000005</v>
@@ -6334,8 +6334,8 @@
       <c r="B26" s="3">
         <v>1003</v>
       </c>
-      <c r="C26" s="5">
-        <v>45839</v>
+      <c r="C26" s="6">
+        <v>45850</v>
       </c>
       <c r="D26" s="3">
         <v>0.83333333300000001</v>
@@ -6372,8 +6372,8 @@
       <c r="B27" s="3">
         <v>1007</v>
       </c>
-      <c r="C27" s="5">
-        <v>45839</v>
+      <c r="C27" s="6">
+        <v>45850</v>
       </c>
       <c r="D27" s="3">
         <v>0.84722222199999997</v>
@@ -6410,8 +6410,8 @@
       <c r="B28" s="3">
         <v>1004</v>
       </c>
-      <c r="C28" s="5">
-        <v>45839</v>
+      <c r="C28" s="6">
+        <v>45850</v>
       </c>
       <c r="D28" s="3">
         <v>0.86111111100000004</v>
@@ -6448,8 +6448,8 @@
       <c r="B29" s="3">
         <v>1002</v>
       </c>
-      <c r="C29" s="5">
-        <v>45839</v>
+      <c r="C29" s="6">
+        <v>45850</v>
       </c>
       <c r="D29" s="3">
         <v>0.875</v>
@@ -6486,8 +6486,8 @@
       <c r="B30" s="3">
         <v>1005</v>
       </c>
-      <c r="C30" s="5">
-        <v>45839</v>
+      <c r="C30" s="6">
+        <v>45850</v>
       </c>
       <c r="D30" s="3">
         <v>0.88888888899999996</v>
@@ -6524,8 +6524,8 @@
       <c r="B31" s="3">
         <v>1006</v>
       </c>
-      <c r="C31" s="5">
-        <v>45839</v>
+      <c r="C31" s="6">
+        <v>45850</v>
       </c>
       <c r="D31" s="3">
         <v>0.90277777800000003</v>
@@ -6909,7 +6909,7 @@
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -6928,7 +6928,7 @@
       <c r="C1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>357</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -6960,7 +6960,7 @@
       <c r="C2" t="s">
         <v>149</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="5">
         <v>45461</v>
       </c>
       <c r="E2" t="s">
@@ -6992,7 +6992,7 @@
       <c r="C3" t="s">
         <v>154</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="5">
         <v>45460</v>
       </c>
       <c r="E3" t="s">
@@ -7024,7 +7024,7 @@
       <c r="C4" t="s">
         <v>168</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="5">
         <v>45462</v>
       </c>
       <c r="E4" t="s">
@@ -7056,7 +7056,7 @@
       <c r="C5" t="s">
         <v>164</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="5">
         <v>45459</v>
       </c>
       <c r="E5" t="s">
@@ -7088,7 +7088,7 @@
       <c r="C6" t="s">
         <v>159</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="5">
         <v>45458</v>
       </c>
       <c r="E6" t="s">
